--- a/data/trans_orig/IP05A03-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP05A03-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>114876</t>
+          <t>114727</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>127488</t>
+          <t>127349</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>128622</t>
+          <t>128689</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>141461</t>
+          <t>141245</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>247741</t>
+          <t>248062</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>265782</t>
+          <t>265692</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,47%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9617</t>
+          <t>9790</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21454</t>
+          <t>21797</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9084</t>
+          <t>9484</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21309</t>
+          <t>20996</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21506</t>
+          <t>21513</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38933</t>
+          <t>37813</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>690</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>5590</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>5103</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7794</t>
+          <t>8151</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>160379</t>
+          <t>161005</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>174339</t>
+          <t>175379</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>175729</t>
+          <t>175281</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>191894</t>
+          <t>192442</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>342895</t>
+          <t>340549</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>362715</t>
+          <t>363300</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,58%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17228</t>
+          <t>16228</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31059</t>
+          <t>30431</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16020</t>
+          <t>16354</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30199</t>
+          <t>31805</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>37595</t>
+          <t>36407</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>56329</t>
+          <t>57823</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,26%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>526</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4847</t>
+          <t>4823</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9368</t>
+          <t>9075</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11702</t>
+          <t>11640</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>100518</t>
+          <t>100899</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>115412</t>
+          <t>115248</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>109794</t>
+          <t>109395</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>125972</t>
+          <t>125370</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>215849</t>
+          <t>215561</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>236074</t>
+          <t>236745</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,48%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19862</t>
+          <t>19617</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33458</t>
+          <t>33814</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19955</t>
+          <t>20765</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35368</t>
+          <t>35709</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43935</t>
+          <t>44142</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63534</t>
+          <t>63916</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6123</t>
+          <t>6188</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>1780</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8742</t>
+          <t>8253</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3620</t>
+          <t>3994</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11999</t>
+          <t>12635</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>143134</t>
+          <t>144724</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>165600</t>
+          <t>165870</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>142751</t>
+          <t>143893</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>163807</t>
+          <t>163771</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>294569</t>
+          <t>293949</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>323778</t>
+          <t>324315</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>78,02%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31767</t>
+          <t>31851</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52380</t>
+          <t>51650</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36596</t>
+          <t>35247</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56345</t>
+          <t>55032</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>72925</t>
+          <t>74287</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>100957</t>
+          <t>101200</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,34%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>6655</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18426</t>
+          <t>18521</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4568</t>
+          <t>4585</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13467</t>
+          <t>13385</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13711</t>
+          <t>13983</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>28377</t>
+          <t>28974</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>537555</t>
+          <t>536907</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>569528</t>
+          <t>570037</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>576466</t>
+          <t>575875</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>609015</t>
+          <t>607924</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1122109</t>
+          <t>1121239</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1169005</t>
+          <t>1168600</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,55%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>91006</t>
+          <t>90003</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>121541</t>
+          <t>121661</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>93234</t>
+          <t>96849</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>124716</t>
+          <t>126016</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>195093</t>
+          <t>193510</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>239113</t>
+          <t>238382</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,04%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12263</t>
+          <t>12340</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26136</t>
+          <t>26411</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12595</t>
+          <t>11982</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26168</t>
+          <t>25957</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27966</t>
+          <t>27496</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>47443</t>
+          <t>47163</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>127650</t>
+          <t>128342</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>136371</t>
+          <t>136372</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>144699</t>
+          <t>144331</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>152429</t>
+          <t>152423</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>276013</t>
+          <t>276045</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>287123</t>
+          <t>287115</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2986</t>
+          <t>2985</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11707</t>
+          <t>11015</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1559</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8954</t>
+          <t>9842</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6353</t>
+          <t>6176</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17111</t>
+          <t>16874</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4787</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>4011</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>177347</t>
+          <t>177731</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>191029</t>
+          <t>191364</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>190346</t>
+          <t>190689</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>205866</t>
+          <t>205987</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>372692</t>
+          <t>374007</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>392840</t>
+          <t>394284</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,79%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10684</t>
+          <t>10586</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22396</t>
+          <t>22582</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14950</t>
+          <t>15044</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29100</t>
+          <t>29377</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>29392</t>
+          <t>28508</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>47937</t>
+          <t>47518</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9827</t>
+          <t>9695</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6647</t>
+          <t>7190</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4247</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13426</t>
+          <t>13639</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>129566</t>
+          <t>130070</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>142713</t>
+          <t>142828</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>137720</t>
+          <t>137461</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>151565</t>
+          <t>151426</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>271277</t>
+          <t>271798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>290484</t>
+          <t>290639</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,27%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11736</t>
+          <t>11470</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24124</t>
+          <t>23752</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14766</t>
+          <t>14797</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27818</t>
+          <t>28813</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29452</t>
+          <t>29644</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48303</t>
+          <t>48602</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4639</t>
+          <t>4618</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>3419</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5863</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>158012</t>
+          <t>158468</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>177633</t>
+          <t>178015</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>155972</t>
+          <t>155087</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>175020</t>
+          <t>174280</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>320520</t>
+          <t>319961</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>346850</t>
+          <t>347412</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,54%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24765</t>
+          <t>24612</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42851</t>
+          <t>43100</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23815</t>
+          <t>24036</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>41843</t>
+          <t>42418</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>53959</t>
+          <t>53498</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>78085</t>
+          <t>79245</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10319</t>
+          <t>10076</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2735</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10700</t>
+          <t>10836</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6568</t>
+          <t>5912</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18410</t>
+          <t>17929</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>609691</t>
+          <t>606861</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>638790</t>
+          <t>636757</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>644218</t>
+          <t>643260</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>673669</t>
+          <t>674148</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1262228</t>
+          <t>1258883</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1303918</t>
+          <t>1300786</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,31%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>58996</t>
+          <t>60812</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>85624</t>
+          <t>89376</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>64624</t>
+          <t>65627</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>93193</t>
+          <t>93439</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>130620</t>
+          <t>133908</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>171065</t>
+          <t>172665</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>6576</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17527</t>
+          <t>17359</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6175</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17865</t>
+          <t>16861</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15504</t>
+          <t>14909</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30582</t>
+          <t>30407</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>121524</t>
+          <t>121507</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>130586</t>
+          <t>130533</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>131714</t>
+          <t>131160</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>141575</t>
+          <t>141364</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>257112</t>
+          <t>257530</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>270772</t>
+          <t>270900</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,47%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3121</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12183</t>
+          <t>12200</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5535</t>
+          <t>5746</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15396</t>
+          <t>15950</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10045</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23705</t>
+          <t>23287</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>172897</t>
+          <t>172721</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>187507</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>187206</t>
+          <t>187194</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>203581</t>
+          <t>203558</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>365609</t>
+          <t>366008</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>387867</t>
+          <t>388522</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,24%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11125</t>
+          <t>11451</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23080</t>
+          <t>23925</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12502</t>
+          <t>13285</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26480</t>
+          <t>27137</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>27470</t>
+          <t>26549</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>45516</t>
+          <t>45317</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,53%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4760</t>
+          <t>4495</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13476</t>
+          <t>13774</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5384</t>
+          <t>4968</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14850</t>
+          <t>14939</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11917</t>
+          <t>11724</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25165</t>
+          <t>24365</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>107850</t>
+          <t>108640</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>124448</t>
+          <t>124381</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>117986</t>
+          <t>117270</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>135667</t>
+          <t>136161</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>230899</t>
+          <t>230368</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>256505</t>
+          <t>254704</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,38%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>19908</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33982</t>
+          <t>33938</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20378</t>
+          <t>21069</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36821</t>
+          <t>37631</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43229</t>
+          <t>44185</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65188</t>
+          <t>65147</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,3%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6782</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17159</t>
+          <t>17264</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6035</t>
+          <t>6042</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16913</t>
+          <t>16636</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15852</t>
+          <t>16079</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>31041</t>
+          <t>30830</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>158526</t>
+          <t>157735</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>177061</t>
+          <t>176782</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>150940</t>
+          <t>150882</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>169770</t>
+          <t>170089</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>316258</t>
+          <t>315723</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>341374</t>
+          <t>342172</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,05%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21311</t>
+          <t>22499</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39149</t>
+          <t>38867</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29388</t>
+          <t>29221</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47826</t>
+          <t>48289</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>55723</t>
+          <t>55574</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>79657</t>
+          <t>80570</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,79%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3461</t>
+          <t>3827</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12814</t>
+          <t>12478</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7577</t>
+          <t>7656</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>6034</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17327</t>
+          <t>16961</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>577559</t>
+          <t>577506</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>608914</t>
+          <t>606699</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>605382</t>
+          <t>605307</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>636797</t>
+          <t>637545</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1191205</t>
+          <t>1192871</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1237713</t>
+          <t>1236750</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,93%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>66127</t>
+          <t>65808</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>93280</t>
+          <t>93197</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>80379</t>
+          <t>81105</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>110195</t>
+          <t>110458</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>154226</t>
+          <t>155021</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>194852</t>
+          <t>193166</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19955</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>36041</t>
+          <t>36276</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16125</t>
+          <t>16688</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32979</t>
+          <t>31880</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,47 +7857,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
+          <t>4,31%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>50621</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>41328</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>64265</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>4,46%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>50621</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>39247</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>63105</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>109438</t>
+          <t>109312</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>115584</t>
+          <t>115676</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>132495</t>
+          <t>132325</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>138871</t>
+          <t>138977</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>245036</t>
+          <t>244527</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>253497</t>
+          <t>253629</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>982</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>544</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>7286</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2685</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10430</t>
+          <t>10810</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3844</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>2457</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>381</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>4187</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>169769</t>
+          <t>168787</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>181843</t>
+          <t>181377</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>228188</t>
+          <t>228020</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>244067</t>
+          <t>243724</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>403265</t>
+          <t>401546</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>422941</t>
+          <t>421945</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,7%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4114</t>
+          <t>4229</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13220</t>
+          <t>13043</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>7845</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20482</t>
+          <t>20993</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>13545</t>
+          <t>13679</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>28759</t>
+          <t>29421</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3158</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11961</t>
+          <t>12352</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11678</t>
+          <t>11884</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>6466</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19904</t>
+          <t>19298</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>86027</t>
+          <t>94285</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>176479</t>
+          <t>176831</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>164057</t>
+          <t>165196</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>177866</t>
+          <t>177665</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>236313</t>
+          <t>248095</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>350136</t>
+          <t>349951</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,7%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11417</t>
+          <t>10836</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>102056</t>
+          <t>94075</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5571</t>
+          <t>5848</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18718</t>
+          <t>17619</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20762</t>
+          <t>21357</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>133341</t>
+          <t>124174</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>33,25%</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4600</t>
+          <t>4673</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>5365</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>437</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7072</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9497,7 +9497,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>136883</t>
+          <t>137175</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>151110</t>
+          <t>151753</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>144128</t>
+          <t>144603</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>161192</t>
+          <t>160669</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>286871</t>
+          <t>287130</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>307614</t>
+          <t>307982</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,6%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12177</t>
+          <t>10969</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25079</t>
+          <t>24322</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12129</t>
+          <t>12409</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25693</t>
+          <t>26320</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26445</t>
+          <t>26618</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45214</t>
+          <t>45258</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>767</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7369</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3276</t>
+          <t>3556</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13272</t>
+          <t>13323</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5960</t>
+          <t>5912</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18091</t>
+          <t>17696</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>509684</t>
+          <t>488058</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>612621</t>
+          <t>612787</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>687322</t>
+          <t>685248</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>713034</t>
+          <t>713032</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1181727</t>
+          <t>1194894</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1315168</t>
+          <t>1316579</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,72%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>37474</t>
+          <t>37386</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>141791</t>
+          <t>169473</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>32099</t>
+          <t>33594</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>55430</t>
+          <t>56782</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>78139</t>
+          <t>78757</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>216185</t>
+          <t>203538</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7394</t>
+          <t>6935</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19097</t>
+          <t>19423</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>7882</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21667</t>
+          <t>22536</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18199</t>
+          <t>18474</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36125</t>
+          <t>36084</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
